--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2505-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2505-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B64443D6-495B-4140-94EF-1EFA8B9CE841}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7D74CA9-2875-47C9-99CF-256F900F4433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{E7E95E12-80A0-4304-B4BB-1B37199EF4DE}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{29152483-9F27-40A1-80FE-CD658C3888F1}"/>
   </bookViews>
   <sheets>
     <sheet name="2505-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1463,25 +1463,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DED164C-BA67-4B98-B42F-8DAB93690BED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2AB57F04-A9E0-476B-89E8-E94ABF7A1F7E}">
   <dimension ref="A1:R50"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="7" width="10.375" customWidth="1"/>
+    <col min="8" max="8" width="9.875" customWidth="1"/>
+    <col min="9" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1509,7 +1509,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1539,7 +1539,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1635,7 +1635,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="40">
         <v>2024</v>
       </c>
@@ -1743,7 +1743,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="38">
         <v>2023</v>
       </c>
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2022</v>
       </c>
@@ -1851,7 +1851,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>25</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>25</v>
       </c>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>25</v>
       </c>
@@ -2019,7 +2019,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="38">
         <v>2021</v>
       </c>
@@ -2073,7 +2073,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>25</v>
       </c>
@@ -2185,7 +2185,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>25</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>3.64</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="40">
         <v>2020</v>
       </c>
@@ -2295,7 +2295,7 @@
         <v>5.27</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>25</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>25</v>
       </c>
@@ -2407,7 +2407,7 @@
         <v>4.79</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>25</v>
       </c>
@@ -2463,7 +2463,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="38">
         <v>2019</v>
       </c>
@@ -2517,7 +2517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="40">
         <v>2018</v>
       </c>
@@ -2571,7 +2571,7 @@
         <v>1.98</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>2017</v>
       </c>
@@ -2625,7 +2625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="40">
         <v>2016</v>
       </c>
@@ -2679,7 +2679,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="38">
         <v>2015</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>1.04</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="40">
         <v>2014</v>
       </c>
@@ -2787,7 +2787,7 @@
         <v>2.81</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="38">
         <v>2013</v>
       </c>
@@ -2841,7 +2841,7 @@
         <v>6.11</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="40">
         <v>2012</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="38">
         <v>2011</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="40">
         <v>2010</v>
       </c>
@@ -3003,7 +3003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="38">
         <v>2009</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="40">
         <v>2008</v>
       </c>
@@ -3111,7 +3111,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38">
         <v>2007</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="40">
         <v>2006</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="38">
         <v>2005</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="40">
         <v>2004</v>
       </c>
@@ -3327,7 +3327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="38">
         <v>2003</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="40">
         <v>2002</v>
       </c>
@@ -3435,7 +3435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="38">
         <v>2001</v>
       </c>
@@ -3489,7 +3489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="40">
         <v>2000</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="38">
         <v>1999</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="40">
         <v>1998</v>
       </c>
@@ -3651,7 +3651,7 @@
         <v>6.9</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="38">
         <v>1997</v>
       </c>
@@ -3705,7 +3705,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="40">
         <v>1996</v>
       </c>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>1995</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="40">
         <v>1994</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="38">
         <v>1993</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="40">
         <v>1992</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="38">
         <v>1991</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="40">
         <v>1990</v>
       </c>
@@ -4083,7 +4083,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="38" t="s">
         <v>39</v>
       </c>
